--- a/data/trans_dic/P36BPD13_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD13_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas</t>
+          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,95; 90,34</t>
+          <t>85,08; 90,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,26; 90,01</t>
+          <t>86,29; 89,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,49; 89,73</t>
+          <t>86,58; 89,62</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,27; 89,03</t>
+          <t>82,45; 89,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,9; 91,66</t>
+          <t>86,96; 91,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,0; 89,56</t>
+          <t>85,06; 89,44</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,9; 88,11</t>
+          <t>81,93; 87,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88,39; 92,52</t>
+          <t>87,84; 92,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,91; 89,7</t>
+          <t>85,87; 89,55</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,77; 88,59</t>
+          <t>83,46; 88,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,75; 90,94</t>
+          <t>87,62; 90,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,1; 88,91</t>
+          <t>86,03; 88,78</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas</t>
+          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>434932; 462561</t>
+          <t>435603; 462948</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>647282; 675399</t>
+          <t>647539; 675240</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1091798; 1132793</t>
+          <t>1093014; 1131336</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1874260; 2028298</t>
+          <t>1878330; 2032768</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1936006; 2042025</t>
+          <t>1937356; 2046409</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3830337; 4035538</t>
+          <t>3832682; 4030364</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>525753; 565611</t>
+          <t>525953; 564537</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>573783; 600590</t>
+          <t>570221; 598736</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1109174; 1158101</t>
+          <t>1108621; 1156177</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2875097; 3040432</t>
+          <t>2864470; 3036856</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3182882; 3298780</t>
+          <t>3178306; 3297920</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6078276; 6276506</t>
+          <t>6073629; 6267719</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36BPD13_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD13_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,08; 90,42</t>
+          <t>85,19; 90,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,29; 89,98</t>
+          <t>86,55; 90,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,58; 89,62</t>
+          <t>86,63; 89,71</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,45; 89,23</t>
+          <t>81,34; 85,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,96; 91,85</t>
+          <t>85,33; 88,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,06; 89,44</t>
+          <t>83,85; 86,18</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,93; 87,94</t>
+          <t>82,42; 88,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,84; 92,23</t>
+          <t>87,68; 91,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,87; 89,55</t>
+          <t>85,84; 89,51</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,21%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,46; 88,48</t>
+          <t>83,23; 86,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,62; 90,92</t>
+          <t>86,68; 88,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,03; 88,78</t>
+          <t>85,32; 87,01</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>450103</t>
+          <t>505979</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>662404</t>
+          <t>721891</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1112506</t>
+          <t>1227870</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>435603; 462948</t>
+          <t>490245; 521497</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>647539; 675240</t>
+          <t>706585; 735449</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1093014; 1131336</t>
+          <t>1205738; 1248715</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1933458</t>
+          <t>1847203</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1977766</t>
+          <t>1875804</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3911224</t>
+          <t>3723007</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1878330; 2032768</t>
+          <t>1804141; 1888057</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1937356; 2046409</t>
+          <t>1842227; 1903521</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3832682; 4030364</t>
+          <t>3670241; 3772107</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>547872</t>
+          <t>606763</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>586591</t>
+          <t>648475</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1134463</t>
+          <t>1255240</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>525953; 564537</t>
+          <t>582597; 624181</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>570221; 598736</t>
+          <t>633980; 663451</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1108621; 1156177</t>
+          <t>1227403; 1279942</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2931434</t>
+          <t>2959946</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3226761</t>
+          <t>3246171</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6158193</t>
+          <t>6206117</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2864470; 3036856</t>
+          <t>2913205; 3011081</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3178306; 3297920</t>
+          <t>3205933; 3279276</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6073629; 6267719</t>
+          <t>6141828; 6263390</t>
         </is>
       </c>
     </row>
